--- a/bases/Wim_Pif/projects/nominee-owners-load/Тестирование/fixtures/web_garant.xlsx
+++ b/bases/Wim_Pif/projects/nominee-owners-load/Тестирование/fixtures/web_garant.xlsx
@@ -23,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>- 614007,Permskiy kray,g Perm,ul Testovaya,d 1,kv 9</t>
   </si>
   <si>
-    <t>WEBFIX_20260916084117_Ivanov Ivan Ivanovich</t>
+    <t>WEBFIX_20260916093503_Ivanov Ivan Ivanovich</t>
   </si>
   <si>
     <t>10</t>
@@ -43,7 +43,25 @@
     <t>6500</t>
   </si>
   <si>
-    <t>01_20260916084117_WEB</t>
+    <t>01_20260916093503_WEB</t>
+  </si>
+  <si>
+    <t>other address 20260916093503</t>
+  </si>
+  <si>
+    <t>WEBFIX_20260916093503_Unknown Petr Petrovich</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>01.06.1991</t>
+  </si>
+  <si>
+    <t>000001</t>
+  </si>
+  <si>
+    <t>01_20260916093503_NONE</t>
   </si>
 </sst>
 </file>
@@ -113,7 +131,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
   </sheetPr>
-  <dimension ref="S3"/>
+  <dimension ref="S4"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="true"/>
@@ -163,6 +181,32 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" ht="11" customHeight="true">
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait" paperSize="9"/>
